--- a/results/log_pv_cap/log_pv_cap_densities_hdensity_tests.xlsx
+++ b/results/log_pv_cap/log_pv_cap_densities_hdensity_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>79.96***</t>
+          <t>73.32***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>39.78***</t>
+          <t>48.22***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7976.69***</t>
+          <t>7701.34***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.50***</t>
+          <t>67.95***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>868.66***</t>
+          <t>665.24***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.96***</t>
+          <t>73.32***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.45***</t>
+          <t>11.51***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6483.40***</t>
+          <t>5508.34***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18.95***</t>
+          <t>17.36***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>868.66***</t>
+          <t>665.24***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>79.96***</t>
+          <t>73.32***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.07***</t>
+          <t>10.86***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6476.39***</t>
+          <t>5493.91***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.69***</t>
+          <t>11.89***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>868.66***</t>
+          <t>665.24***</t>
         </is>
       </c>
     </row>
